--- a/いword.xlsx
+++ b/いword.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B28B76E-C596-449E-9F23-8CD698840893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2218AF7C-B8D1-4578-A5F9-25FD9957BF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="365">
   <si>
     <t>きらい</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -130,10 +130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>さびしい</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>うれしい</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -387,10 +383,6 @@
   </si>
   <si>
     <t>煩い</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>さみしい</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1730,6 +1722,10 @@
   </si>
   <si>
     <t>（强壮的，坚强的）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さみしい／さびしい</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2332,30 +2328,30 @@
   <sheetData>
     <row r="1" spans="1:23" ht="15.6">
       <c r="D1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="U1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="18">
       <c r="A2" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>1</v>
@@ -2364,18 +2360,18 @@
         <v>0</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="O2" s="9" t="s">
         <v>13</v>
@@ -2384,10 +2380,10 @@
         <v>12</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="S2" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="U2" s="1" t="s">
         <v>20</v>
@@ -2410,16 +2406,16 @@
         <v>3</v>
       </c>
       <c r="G3" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="K3" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O3" s="27" t="s">
         <v>15</v>
@@ -2428,13 +2424,13 @@
         <v>14</v>
       </c>
       <c r="R3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="T3" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="U3" t="s">
         <v>6</v>
@@ -2445,100 +2441,100 @@
     </row>
     <row r="4" spans="1:23" ht="18">
       <c r="A4" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="G4" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="I4" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="9" t="s">
         <v>2</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="O4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="R4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="S4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="S4" s="7" t="s">
-        <v>84</v>
-      </c>
       <c r="U4" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="71.400000000000006">
       <c r="A5" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>90</v>
+        <v>364</v>
       </c>
       <c r="G5" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>82</v>
-      </c>
       <c r="K5" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="M5" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="O5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="Q5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q5" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="R5" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="V5" s="1" t="s">
         <v>16</v>
@@ -2546,46 +2542,46 @@
     </row>
     <row r="6" spans="1:23" ht="18">
       <c r="A6" s="19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>24</v>
+        <v>364</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="L6" s="10" t="s">
-        <v>72</v>
-      </c>
       <c r="O6" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P6" s="10" t="s">
         <v>3</v>
       </c>
       <c r="R6" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S6" s="10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="U6" t="s">
         <v>8</v>
@@ -2596,39 +2592,39 @@
     </row>
     <row r="7" spans="1:23" ht="18">
       <c r="A7" s="22" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R7" s="10" t="s">
         <v>20</v>
@@ -2645,46 +2641,46 @@
     </row>
     <row r="8" spans="1:23" ht="18">
       <c r="A8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="B8" t="s">
-        <v>254</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>255</v>
-      </c>
       <c r="D8" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I8" t="s">
         <v>146</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="I8" t="s">
-        <v>148</v>
-      </c>
       <c r="K8" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="P8" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="R8" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="U8" t="s">
         <v>18</v>
@@ -2695,44 +2691,44 @@
     </row>
     <row r="9" spans="1:23" ht="18">
       <c r="A9" s="22" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="G9" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H9" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>151</v>
       </c>
       <c r="J9" s="8"/>
       <c r="O9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="P9" s="9" t="s">
-        <v>34</v>
-      </c>
       <c r="R9" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="T9" t="s">
         <v>175</v>
-      </c>
-      <c r="S9" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="T9" t="s">
-        <v>177</v>
       </c>
       <c r="U9" s="4" t="s">
         <v>17</v>
@@ -2743,679 +2739,679 @@
     </row>
     <row r="10" spans="1:23" ht="18">
       <c r="A10" s="22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="7"/>
       <c r="O10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="P10" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="Q10" s="8"/>
       <c r="R10" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V10" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="18">
       <c r="A11" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="P11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="Q11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="Q11" s="9" t="s">
-        <v>48</v>
-      </c>
       <c r="R11" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="T11" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="S11" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="T11" s="9" t="s">
-        <v>306</v>
-      </c>
       <c r="U11" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="V11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="W11" s="14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="18">
       <c r="A12" s="10" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G12" s="8"/>
       <c r="O12" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="18">
       <c r="A13" s="26" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G13" s="8"/>
       <c r="O13" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q13" s="8"/>
       <c r="U13" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="V13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="18">
       <c r="A14" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>136</v>
-      </c>
       <c r="D14" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q14" s="8"/>
       <c r="U14" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="18">
       <c r="A15" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C15" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O15" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="Q15" s="8"/>
       <c r="U15" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="18">
       <c r="A16" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>113</v>
       </c>
       <c r="G16" s="7"/>
       <c r="O16" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="P16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q16" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="P16" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q16" s="10" t="s">
-        <v>80</v>
-      </c>
       <c r="U16" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="V16" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="18">
       <c r="A17" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="O17" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P17" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="P17" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="Q17" s="8"/>
     </row>
     <row r="18" spans="1:17" ht="18">
       <c r="A18" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>309</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>311</v>
-      </c>
       <c r="D18" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P18" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q18" s="8"/>
     </row>
     <row r="19" spans="1:17" ht="18">
       <c r="D19" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F19" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G19" s="8"/>
       <c r="O19" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Q19" s="8"/>
     </row>
     <row r="20" spans="1:17" ht="18">
       <c r="D20" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="O20" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="P20" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q20" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="P20" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="18">
       <c r="D21" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q21" s="18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="18">
       <c r="D22" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G22" s="8"/>
       <c r="O22" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="P22" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="P22" s="10" t="s">
-        <v>120</v>
       </c>
       <c r="Q22" s="8"/>
     </row>
     <row r="23" spans="1:17" ht="18">
       <c r="D23" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G23" s="13"/>
       <c r="O23" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Q23" s="8"/>
     </row>
     <row r="24" spans="1:17" ht="18">
       <c r="D24" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G24" s="17"/>
       <c r="O24" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="P24" s="10" t="s">
         <v>119</v>
-      </c>
-      <c r="P24" s="10" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="18">
       <c r="D25" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="18">
       <c r="D26" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="O26" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="P26" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="P26" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="Q26" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="18">
       <c r="D27" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G27" s="7"/>
       <c r="O27" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q27" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="P27" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q27" s="8" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="18">
       <c r="D28" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>244</v>
-      </c>
       <c r="O28" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q28" s="7" t="s">
         <v>256</v>
-      </c>
-      <c r="P28" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q28" s="7" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="18">
       <c r="D29" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F29" s="8"/>
       <c r="O29" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q29" s="7"/>
     </row>
     <row r="30" spans="1:17" ht="18">
       <c r="D30" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G30" s="17"/>
       <c r="O30" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="18">
       <c r="D31" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="18">
       <c r="D32" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="E32" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>203</v>
-      </c>
       <c r="O32" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" spans="4:17" ht="18">
       <c r="D33" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F33" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>216</v>
-      </c>
       <c r="O33" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" spans="4:17" ht="18">
       <c r="D34" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F34" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>220</v>
-      </c>
       <c r="O34" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="4:17" ht="18">
       <c r="D35" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>252</v>
-      </c>
       <c r="O35" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="4:17" ht="18">
       <c r="D36" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="O36" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P36" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="4:17" ht="18">
       <c r="D37" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="F37" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F37" s="29" t="s">
-        <v>269</v>
-      </c>
       <c r="O37" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="38" spans="4:17" ht="18">
       <c r="D38" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F38" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="F38" s="29" t="s">
-        <v>273</v>
-      </c>
       <c r="O38" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="P38" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q38" s="7" t="s">
         <v>360</v>
-      </c>
-      <c r="Q38" s="7" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="39" spans="4:17" ht="18">
       <c r="D39" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F39" s="29" t="s">
         <v>275</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="F39" s="29" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="40" spans="4:17" ht="18">
       <c r="D40" t="s">
+        <v>328</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="F40" s="29" t="s">
         <v>330</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F40" s="29" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="41" spans="4:17" ht="18">
       <c r="D41" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="F41" s="29" t="s">
         <v>363</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F41" s="29" t="s">
-        <v>365</v>
       </c>
       <c r="G41" s="8"/>
     </row>
@@ -3446,212 +3442,212 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18">
       <c r="A1" s="7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18">
       <c r="A2" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F2" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="G2" t="s">
         <v>350</v>
       </c>
-      <c r="G2" t="s">
-        <v>352</v>
-      </c>
       <c r="H2" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18">
       <c r="A3" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="18">
       <c r="A4" s="7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18">
       <c r="A5" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18">
       <c r="A6" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" t="s">
         <v>321</v>
       </c>
-      <c r="B6" t="s">
-        <v>323</v>
-      </c>
       <c r="C6" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18">
       <c r="A7" s="7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18">
       <c r="A8" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18">
       <c r="A9" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18">
       <c r="A10" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>312</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="18">
       <c r="A11" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" t="s">
         <v>315</v>
       </c>
-      <c r="B11" t="s">
-        <v>317</v>
-      </c>
       <c r="C11" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18">
       <c r="A12" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B12" t="s">
         <v>318</v>
       </c>
-      <c r="B12" t="s">
-        <v>320</v>
-      </c>
       <c r="C12" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="18">
       <c r="A13" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B13" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="18">
       <c r="A14" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B14" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="18">
       <c r="A15" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B15" t="s">
         <v>333</v>
       </c>
-      <c r="B15" t="s">
-        <v>335</v>
-      </c>
       <c r="C15" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="18">
       <c r="A16" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18">
       <c r="A17" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B17" t="s">
         <v>339</v>
       </c>
-      <c r="B17" t="s">
-        <v>341</v>
-      </c>
       <c r="C17" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18">
       <c r="A18" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B18" t="s">
         <v>353</v>
       </c>
-      <c r="B18" t="s">
-        <v>355</v>
-      </c>
       <c r="C18" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
